--- a/题库/PY程序设计模拟题1.xlsx
+++ b/题库/PY程序设计模拟题1.xlsx
@@ -294,6 +294,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11.5"/>
+        <color rgb="FF0F1115"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
       <t>执行下列</t>
     </r>
     <r>
@@ -376,7 +382,7 @@
     <t>a='Python'，表达式 a[:2]的结果为("【1】")。</t>
   </si>
   <si>
-    <t>Pto</t>
+    <t>Py</t>
   </si>
   <si>
     <r>
